--- a/outputs/daily/hr_rankings_2026-08-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18.xlsx
@@ -1852,34 +1852,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2834,34 +2830,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4302,7 +4294,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6940,7 +6932,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10826,7 +10818,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -11810,7 +11802,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -15792,34 +15784,30 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22458,34 +22446,30 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24200,7 +24184,7 @@
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
@@ -31254,34 +31238,30 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31740,7 +31720,7 @@
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr">
@@ -37158,7 +37138,7 @@
       </c>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr">
@@ -40952,7 +40932,7 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr">
@@ -45416,7 +45396,7 @@
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr">
@@ -45730,7 +45710,7 @@
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr">
@@ -47446,34 +47426,30 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48078,34 +48054,30 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48878,7 +48850,7 @@
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr">
@@ -49696,34 +49668,30 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC155" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52244,34 +52212,30 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC163" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD163" t="inlineStr"/>
       <c r="AE163" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57780,7 +57744,7 @@
       </c>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr">
@@ -69094,7 +69058,7 @@
       </c>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr">
@@ -73164,7 +73128,7 @@
       </c>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr">
@@ -78176,7 +78140,7 @@
       </c>
       <c r="BI245" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ245" t="inlineStr">
@@ -78804,7 +78768,7 @@
       </c>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr">
@@ -83192,7 +83156,7 @@
       </c>
       <c r="BI261" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ261" t="inlineStr">
@@ -87818,34 +87782,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -88800,34 +88760,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -89954,7 +89910,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -90268,7 +90224,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -92906,7 +92862,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
